--- a/artfynd/A 43954-2023 artfynd.xlsx
+++ b/artfynd/A 43954-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117644595</v>
+        <v>117644169</v>
       </c>
       <c r="B2" t="n">
-        <v>91064</v>
+        <v>79561</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584927</v>
+        <v>584848</v>
       </c>
       <c r="R2" t="n">
-        <v>7054812</v>
+        <v>7054851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117644169</v>
+        <v>117644595</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>91064</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584848</v>
+        <v>584927</v>
       </c>
       <c r="R4" t="n">
-        <v>7054851</v>
+        <v>7054812</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 43954-2023 artfynd.xlsx
+++ b/artfynd/A 43954-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117644169</v>
+        <v>117644265</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Flöjmyran (Flöjmyran), Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584848</v>
+        <v>584865</v>
       </c>
       <c r="R2" t="n">
-        <v>7054851</v>
+        <v>7054842</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117644265</v>
+        <v>117644595</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>91066</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Flöjmyran (Flöjmyran), Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584865</v>
+        <v>584927</v>
       </c>
       <c r="R3" t="n">
-        <v>7054842</v>
+        <v>7054812</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117644595</v>
+        <v>117644169</v>
       </c>
       <c r="B4" t="n">
-        <v>91064</v>
+        <v>79563</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584927</v>
+        <v>584848</v>
       </c>
       <c r="R4" t="n">
-        <v>7054812</v>
+        <v>7054851</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,7 +1019,7 @@
         <v>117644229</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
